--- a/组合实盘追踪/20260525_银河.xlsx
+++ b/组合实盘追踪/20260525_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>700.2</v>
+        <v>707.8</v>
       </c>
       <c r="D2" s="1">
-        <v>1.2</v>
+        <v>8.8</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-10.9</v>
+        <v>-3.3</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0153</v>
+        <v>-0.0046</v>
       </c>
       <c r="L2" s="1">
-        <v>-10.9</v>
+        <v>-3.3</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0153</v>
+        <v>-0.0046</v>
       </c>
       <c r="N2" s="1">
-        <v>4.6</v>
+        <v>12.8</v>
       </c>
       <c r="O2" s="1">
-        <v>-11.1</v>
+        <v>-3.3</v>
       </c>
       <c r="P2" s="1">
-        <v>-11.1</v>
+        <v>-3.3</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0239</v>
+        <v>0.0241</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>11</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="U2" s="5">
-        <v>3.501</v>
+        <v>3.539</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0157</v>
+        <v>0.0048</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0526</v>
+        <v>0.064</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0539</v>
+        <v>0.0653</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.2244</v>
+        <v>0.2377</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4756</v>
+        <v>0.4916</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>838</v>
+        <v>822.4</v>
       </c>
       <c r="D3" s="1">
-        <v>4.4</v>
+        <v>-11.2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0053</v>
+        <v>-0.0134</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-24.9</v>
+        <v>-40.5</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0289</v>
+        <v>-0.0469</v>
       </c>
       <c r="L3" s="1">
-        <v>-24.9</v>
+        <v>-40.5</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0289</v>
+        <v>-0.0469</v>
       </c>
       <c r="N3" s="1">
-        <v>6.8</v>
+        <v>-8.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-24.1</v>
+        <v>-40.5</v>
       </c>
       <c r="P3" s="1">
-        <v>-24.1</v>
+        <v>-40.5</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0286</v>
+        <v>0.0281</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>11</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0053</v>
+        <v>-0.0134</v>
       </c>
       <c r="U3" s="5">
-        <v>2.095</v>
+        <v>2.056</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0296</v>
+        <v>0.0491</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0141</v>
+        <v>-0.0325</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.047</v>
+        <v>0.0275</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0444</v>
+        <v>0.0249</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0906</v>
+        <v>0.0703</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>695.2</v>
+        <v>699.6</v>
       </c>
       <c r="D4" s="1">
-        <v>-6.6</v>
+        <v>-2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0094</v>
+        <v>-0.0031</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-41.9</v>
+        <v>-37.5</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0569</v>
+        <v>-0.0509</v>
       </c>
       <c r="L4" s="1">
-        <v>-41.9</v>
+        <v>-37.5</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0569</v>
+        <v>-0.0509</v>
       </c>
       <c r="N4" s="1">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1">
-        <v>-40.8</v>
+        <v>-37.5</v>
       </c>
       <c r="P4" s="1">
-        <v>-40.8</v>
+        <v>-37.5</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0237</v>
+        <v>0.0239</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>11</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0094</v>
+        <v>-0.0031</v>
       </c>
       <c r="U4" s="5">
-        <v>0.632</v>
+        <v>0.636</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0601</v>
+        <v>0.0535</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0202</v>
+        <v>-0.014</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1023</v>
+        <v>-0.0966</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1749</v>
+        <v>-0.1697</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1234</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>974.8</v>
+        <v>987.4</v>
       </c>
       <c r="D5" s="1">
-        <v>2.4</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0025</v>
+        <v>0.0154</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-16.5</v>
+        <v>-3.9</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0166</v>
+        <v>-0.0039</v>
       </c>
       <c r="L5" s="1">
-        <v>-16.5</v>
+        <v>-3.9</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0166</v>
+        <v>-0.0039</v>
       </c>
       <c r="N5" s="1">
-        <v>7.8</v>
+        <v>20.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-16.9</v>
+        <v>-3.9</v>
       </c>
       <c r="P5" s="1">
-        <v>-16.9</v>
+        <v>-3.9</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0333</v>
+        <v>0.0337</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>11</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0025</v>
+        <v>0.0154</v>
       </c>
       <c r="U5" s="5">
-        <v>4.874</v>
+        <v>4.937</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.017</v>
+        <v>0.0041</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0192</v>
+        <v>0.0324</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0335</v>
+        <v>0.0469</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0973</v>
+        <v>0.1115</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2823</v>
+        <v>0.2988</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>952</v>
+        <v>951.2</v>
       </c>
       <c r="D6" s="1">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0062</v>
+        <v>0.0054</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0223</v>
+        <v>-0.0231</v>
       </c>
       <c r="L6" s="1">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0223</v>
+        <v>-0.0231</v>
       </c>
       <c r="N6" s="1">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="O6" s="1">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="P6" s="1">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0325</v>
+        <v>0.0324</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>11</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0062</v>
+        <v>0.0054</v>
       </c>
       <c r="U6" s="5">
-        <v>9.52</v>
+        <v>9.512</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0228</v>
+        <v>0.0237</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0311</v>
+        <v>-0.0319</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1306</v>
+        <v>-0.1313</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0749</v>
+        <v>0.074</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2772</v>
+        <v>0.2761</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>785</v>
+        <v>806.8</v>
       </c>
       <c r="D8" s="1">
-        <v>-4.2</v>
+        <v>17.6</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0053</v>
+        <v>0.0223</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-1.7</v>
+        <v>20.1</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0022</v>
+        <v>0.0255</v>
       </c>
       <c r="L8" s="1">
-        <v>-1.7</v>
+        <v>20.1</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0022</v>
+        <v>0.0255</v>
       </c>
       <c r="N8" s="1">
-        <v>2.8</v>
+        <v>24.2</v>
       </c>
       <c r="O8" s="1">
-        <v>-1.3</v>
+        <v>20.1</v>
       </c>
       <c r="P8" s="1">
-        <v>-1.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0268</v>
+        <v>0.0275</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>11</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0053</v>
+        <v>0.0223</v>
       </c>
       <c r="U8" s="5">
-        <v>3.925</v>
+        <v>4.034</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0023</v>
+        <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0683</v>
+        <v>0.098</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1912</v>
+        <v>0.2243</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3497</v>
+        <v>0.3872</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9684</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19824</v>
+        <v>19821.2</v>
       </c>
       <c r="D9" s="1">
-        <v>37.8</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-553.64</v>
+        <v>-556.44</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0272</v>
+        <v>-0.0273</v>
       </c>
       <c r="L9" s="1">
-        <v>-553.64</v>
+        <v>-556.44</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0272</v>
+        <v>-0.0273</v>
       </c>
       <c r="N9" s="1">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="O9" s="1">
-        <v>-570.44</v>
+        <v>-556.44</v>
       </c>
       <c r="P9" s="1">
-        <v>-570.44</v>
+        <v>-556.44</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6766</v>
+        <v>0.6761</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>11</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="U9" s="5">
-        <v>14.16</v>
+        <v>14.158</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0279</v>
+        <v>0.028</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.006</v>
+        <v>-0.0061</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0393</v>
+        <v>-0.0394</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0524</v>
+        <v>0.0523</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1812</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>643.6</v>
+        <v>632</v>
       </c>
       <c r="D10" s="1">
-        <v>-4.8</v>
+        <v>-16.4</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0074</v>
+        <v>-0.0253</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-28.5</v>
+        <v>-40.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0424</v>
+        <v>-0.0597</v>
       </c>
       <c r="L10" s="1">
-        <v>-28.5</v>
+        <v>-40.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0424</v>
+        <v>-0.0597</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.8</v>
+        <v>-11.6</v>
       </c>
       <c r="O10" s="1">
-        <v>-30.1</v>
+        <v>-40.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-30.1</v>
+        <v>-40.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.022</v>
+        <v>0.0216</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>11</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0074</v>
+        <v>-0.0253</v>
       </c>
       <c r="U10" s="5">
-        <v>1.609</v>
+        <v>1.58</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0441</v>
+        <v>0.0633</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.0319</v>
+        <v>-0.0494</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2264</v>
+        <v>0.2043</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3265</v>
+        <v>0.3026</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2483</v>
+        <v>0.2258</v>
       </c>
     </row>
     <row r="11">
@@ -1312,13 +1312,13 @@
         <v>0.0055</v>
       </c>
       <c r="N11" s="1">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O11" s="1">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="P11" s="1">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0295</v>
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29296.6</v>
+        <v>29312.2</v>
       </c>
       <c r="D12" s="1">
-        <v>38.2</v>
+        <v>53.8</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0013</v>
+        <v>0.0018</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-695.19</v>
+        <v>-679.59</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0232</v>
+        <v>-0.0227</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>51.4</v>
+        <v>57.8</v>
       </c>
       <c r="O12" s="1">
-        <v>-711.49</v>
+        <v>-679.59</v>
       </c>
       <c r="P12" s="1">
-        <v>-711.49</v>
+        <v>-679.59</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9999</v>
